--- a/04_quality_assessment/quality_assessment.xlsx
+++ b/04_quality_assessment/quality_assessment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Quality Assessment" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Rubric" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality_Assessment" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rubric" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,21 +28,14 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -57,10 +50,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -427,20 +423,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="26.1" customWidth="1" min="2" max="2"/>
+    <col width="10.8" customWidth="1" min="3" max="3"/>
+    <col width="12.6" customWidth="1" min="4" max="4"/>
+    <col width="13.5" customWidth="1" min="5" max="5"/>
+    <col width="17.1" customWidth="1" min="6" max="6"/>
+    <col width="23.4" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15.3" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="70" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,142 +447,342 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>q1_clear_research_question</t>
+          <t>label</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>q2_methodology_described</t>
+          <t>q1_objective</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>q3_validity_threats_discussed</t>
+          <t>q2_methodology</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>q4_results_support_conclusions</t>
+          <t>q3_data_sources</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>q5_relevance_to_multicloud_governance</t>
+          <t>q4_analytical_depth</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>total_score</t>
+          <t>q5_validity_of_conclusions</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>quality_tier</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>meets_threshold_6</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>assessed_by</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>assessment_date</t>
-        </is>
-      </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>STU-0001</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>TEMPLATE Assessor</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>EXAMPLE row - replace with real quality appraisal</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>STU-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Yeboah-Ofori et al. (2024)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Item scores not archived in v1; all ten studies passed the &gt;=6/10 threshold per ETECOM 2026. To be re-scored in the journal extension.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>STU-0002</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>TEMPLATE Assessor</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>EXAMPLE row - replace with real quality appraisal</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>STU-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Hegde et al. (2023)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Item scores not archived in v1; all ten studies passed the &gt;=6/10 threshold per ETECOM 2026. To be re-scored in the journal extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>STU-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Diningrat et al. (2025)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Item scores not archived in v1; all ten studies passed the &gt;=6/10 threshold per ETECOM 2026. To be re-scored in the journal extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>STU-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Aljarrah et al. (2024)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Item scores not archived in v1; all ten studies passed the &gt;=6/10 threshold per ETECOM 2026. To be re-scored in the journal extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>STU-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Cuzzocrea &amp; Belmerabet (2024)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Item scores not archived in v1; all ten studies passed the &gt;=6/10 threshold per ETECOM 2026. To be re-scored in the journal extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>STU-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Kaur et al. (2024)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Item scores not archived in v1; all ten studies passed the &gt;=6/10 threshold per ETECOM 2026. To be re-scored in the journal extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>STU-07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Alouffi et al. (2021)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Item scores not archived in v1; all ten studies passed the &gt;=6/10 threshold per ETECOM 2026. To be re-scored in the journal extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>STU-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Ali et al. (2025)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Item scores not archived in v1; all ten studies passed the &gt;=6/10 threshold per ETECOM 2026. To be re-scored in the journal extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>STU-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>AlGhamdi et al. (2020)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Item scores not archived in v1; all ten studies passed the &gt;=6/10 threshold per ETECOM 2026. To be re-scored in the journal extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>STU-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Pöhn &amp; Hillmann (2021)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Item scores not archived in v1; all ten studies passed the &gt;=6/10 threshold per ETECOM 2026. To be re-scored in the journal extension.</t>
         </is>
       </c>
     </row>
@@ -601,144 +797,166 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="37.8" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="70" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>criterion_id</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>scoring_scale</t>
+          <t>scale</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>guidance</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>q1_clear_research_question</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Clear research question(s)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0 = No, 0.5 = Partially, 1 = Yes</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TEMPLATE - does the study state an explicit research question/objective?</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Clarity of research objective</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2 = explicit scope; 1 = imprecise; 0 = absent</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>q2_methodology_described</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Methodology clearly described</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0 = No, 0.5 = Partially, 1 = Yes</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>TEMPLATE - is the research method (design, data collection) described in enough detail to assess rigor?</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Appropriateness and rigour of methodology</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2 = explicit and suitable; 1 = partially appropriate; 0 = absent/inappropriate</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>q3_validity_threats_discussed</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Validity threats discussed</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0 = No, 0.5 = Partially, 1 = Yes</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>TEMPLATE - does the study discuss limitations/threats to validity?</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Quality/credibility of data sources</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2 = peer-reviewed and clearly identified; 1 = mixed quality; 0 = non-peer-reviewed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>q4_results_support_conclusions</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Results support conclusions</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0 = No, 0.5 = Partially, 1 = Yes</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TEMPLATE - are the conclusions adequately supported by the presented results?</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Analytical depth and critical contribution</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2 = substantive; 1 = some; 0 = purely descriptive</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>q5_relevance_to_multicloud_governance</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Relevance to multi-cloud governance</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0 = No, 0.5 = Partially, 1 = Yes</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>TEMPLATE - how directly does the study address multi-cloud governance (vs. tangential)?</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Validity of conclusions</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2 = well supported; 1 = partially supported; 0 = poorly supported/overreaching</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Inclusion threshold</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>&gt;= 6/10; normative documents exempt</t>
         </is>
       </c>
     </row>
